--- a/data/PortWatch_28_geometry_registry.xlsx
+++ b/data/PortWatch_28_geometry_registry.xlsx
@@ -5,25 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d49dd70d4980b0a9/Desktop/Thesis/Dataset/chokepoints geometry/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d49dd70d4980b0a9/Desktop/Thesis/code/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_5F2205E569E4AE00944577EE73BABFF5B7D453DA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9AB66A6-6B41-4995-926D-B6A33F54D47D}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_5F2205E569E4AE00944577EE73BABFF5B7D453DA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09315D35-6959-48C5-8B7A-7223ACAC0F27}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Geometry Registry" sheetId="1" r:id="rId1"/>
     <sheet name="Sources &amp; Decisions" sheetId="2" r:id="rId2"/>
-    <sheet name="README" sheetId="3" r:id="rId3"/>
-    <sheet name="Block 1 Validation" sheetId="4" r:id="rId4"/>
-    <sheet name="Block 2 Validation" sheetId="5" r:id="rId5"/>
-    <sheet name="Block 3 Validation" sheetId="6" r:id="rId6"/>
-    <sheet name="Tsugaru Refinement" sheetId="7" r:id="rId7"/>
-    <sheet name="Derived Geometry Summary" sheetId="8" r:id="rId8"/>
+    <sheet name="Derived Geometry Summary" sheetId="8" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Derived Geometry Summary'!$A$1:$K$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Derived Geometry Summary'!$A$1:$K$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Geometry Registry'!$A$1:$V$29</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -31,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="288">
   <si>
     <t>node_id</t>
   </si>
@@ -228,15 +223,9 @@
     <t>Malacca Strait</t>
   </si>
   <si>
-    <t>Yes — detailed Marine Regions geometry</t>
-  </si>
-  <si>
     <t>MultiPolygon (detailed source geometry)</t>
   </si>
   <si>
-    <t>FINAL — detailed Marine Regions IHO geometry loaded</t>
-  </si>
-  <si>
     <t>No replacement needed; retain source geometry and citation</t>
   </si>
   <si>
@@ -315,9 +304,6 @@
     <t>Dover Strait</t>
   </si>
   <si>
-    <t>FINAL — detailed Marine Regions SeaVoX geometry loaded</t>
-  </si>
-  <si>
     <t>https://www.marineregions.org/gazetteer.php?id=24196&amp;p=details</t>
   </si>
   <si>
@@ -780,18 +766,12 @@
     <t>Do not infer that all Point features are transit geometries. Points are placeholders until a polygon/corridor is sourced; fallback buffers must be separately calibrated and documented.</t>
   </si>
   <si>
-    <t>Marine Regions — IHO Sea Areas v3</t>
-  </si>
-  <si>
     <t>Interim envelopes for Malacca, Gibraltar, Makassar; MRGIDs 4275, 3346, 4339. Detailed polygons available via Marine Regions WFS/download service.</t>
   </si>
   <si>
     <t>https://www.marineregions.org/sources.php</t>
   </si>
   <si>
-    <t>Marine Regions — SeaVoX v19</t>
-  </si>
-  <si>
     <t>Marine Regions WFS</t>
   </si>
   <si>
@@ -801,9 +781,6 @@
     <t>https://www.marineregions.org/webservices.php</t>
   </si>
   <si>
-    <t>Marine Regions — Detailed geometries received</t>
-  </si>
-  <si>
     <t>Detailed MultiPolygon GeoJSON loaded for Malacca Strait (4275), Strait of Gibraltar (3346), and Makassar Strait (4339).</t>
   </si>
   <si>
@@ -828,9 +805,6 @@
     <t>5 km buffer around an operational strait centerline. Constructed for route-transit classification only; not presented as an official geographic boundary.</t>
   </si>
   <si>
-    <t>BLOCK 1 v7 — official routeing geometries</t>
-  </si>
-  <si>
     <t>IMO official routeing measure</t>
   </si>
   <si>
@@ -858,234 +832,15 @@
     <t>Three TSS components reconstructed from outer traffic-lane boundaries.</t>
   </si>
   <si>
-    <t>PORTWATCH 28 – GEOMETRY WORKING REGISTRY</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Working, traceable geometry file for the 28 PortWatch chokepoints.</t>
-  </si>
-  <si>
-    <t>Ready now</t>
-  </si>
-  <si>
-    <t>3 published polygons: Suez, Bab el-Mandeb, Cape of Good Hope.</t>
-  </si>
-  <si>
-    <t>Important</t>
-  </si>
-  <si>
-    <t>The remaining 25 features are PortWatch POINT placeholders, not final chokepoint areas.</t>
-  </si>
-  <si>
-    <t>Next</t>
-  </si>
-  <si>
-    <t>Replace placeholders with sourced polygon/corridor geometries. Marine Regions candidates already confirmed for Malacca, Gibraltar, Dover and Makassar.</t>
-  </si>
-  <si>
-    <t>CRS</t>
-  </si>
-  <si>
-    <t>EPSG:4326 / WGS84</t>
-  </si>
-  <si>
-    <t>v2 update</t>
-  </si>
-  <si>
-    <t>Malacca, Strait of Gibraltar, Dover and Makassar now have Polygon geometries derived from the official Marine Regions published spatial extents (min/max coordinates). These are interim bounding envelopes, not the detailed source polygons. They must remain flagged as non-final until the WFS/source polygon is retrieved.</t>
-  </si>
-  <si>
-    <t>v3 update</t>
-  </si>
-  <si>
-    <t>Replaced interim bounding envelopes with detailed Marine Regions MultiPolygon geometries for Malacca, Gibraltar and Makassar. Dover remains interim because the prior WFS query used the wrong MRGID; corrected MRGID is 24196.</t>
-  </si>
-  <si>
-    <t>v5 update</t>
-  </si>
-  <si>
-    <t>Hormuz replaced by detailed Marine Regions/SeaVoX MultiPolygon (mrgid_sr 24076). Panama and Bosporus replaced by explicitly derived operational corridor polygons for transit classification.</t>
-  </si>
-  <si>
-    <t>Chokepoint</t>
-  </si>
-  <si>
-    <t>Geometry used</t>
-  </si>
-  <si>
-    <t>Authority</t>
-  </si>
-  <si>
-    <t>Document</t>
-  </si>
-  <si>
-    <t>Geographic cross-reference</t>
-  </si>
-  <si>
-    <t>Methodological status</t>
-  </si>
-  <si>
-    <t>Validation note</t>
-  </si>
-  <si>
-    <t>Source URL</t>
-  </si>
-  <si>
-    <t>Polygon: official two-way route B–C</t>
-  </si>
-  <si>
-    <t>IMO</t>
-  </si>
-  <si>
-    <t>NCSR 5/3/7</t>
-  </si>
-  <si>
-    <t>Marine Regions MRGID 24122</t>
-  </si>
-  <si>
-    <t>FINAL — OFFICIAL ROUTEING GEOMETRY</t>
-  </si>
-  <si>
-    <t>Uses the IMO route segment through the strait, rather than a generic point buffer.</t>
-  </si>
-  <si>
-    <t>Polygon: Prince of Wales Channel two-way route</t>
-  </si>
-  <si>
-    <t>SN.1/Circ.326</t>
-  </si>
-  <si>
-    <t>Marine Regions MRGID 4362 (gazetteer point)</t>
-  </si>
-  <si>
-    <t>Uses complete published northern and southern WGS84 route limits.</t>
-  </si>
-  <si>
-    <t>MultiPolygon: two TSS sections</t>
-  </si>
-  <si>
-    <t>COLREG.2/Circ.74</t>
-  </si>
-  <si>
-    <t>Marine Regions MRGID 24127</t>
-  </si>
-  <si>
-    <t>FINAL — OFFICIAL TSS GEOMETRY</t>
-  </si>
-  <si>
-    <t>Uses outer traffic-lane boundaries of both published TSS components.</t>
-  </si>
-  <si>
-    <t>MultiPolygon: three TSS sections</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>Uses outer traffic-lane boundaries of all three published TSS components.</t>
-  </si>
-  <si>
-    <t>Marine Regions MRGID</t>
-  </si>
-  <si>
-    <t>source type</t>
-  </si>
-  <si>
-    <t>geometry status</t>
-  </si>
-  <si>
-    <t>gate azimuth (deg)</t>
-  </si>
-  <si>
     <t>span km</t>
   </si>
   <si>
     <t>thickness km</t>
   </si>
   <si>
-    <t>sensitivity test</t>
-  </si>
-  <si>
     <t>source URL</t>
   </si>
   <si>
-    <t>validation note</t>
-  </si>
-  <si>
-    <t>DERIVED</t>
-  </si>
-  <si>
-    <t>±25% on span and thickness</t>
-  </si>
-  <si>
-    <t>Derived operational crossing gate centered on PortWatch point; N-S gate across the E-W strait, 55 km span x 8 km thickness.</t>
-  </si>
-  <si>
-    <t>reference ID</t>
-  </si>
-  <si>
-    <t>https://www.marineregions.org/documents/bulletin69e.pdf</t>
-  </si>
-  <si>
-    <t>Derived N-S crossing gate centered on PortWatch point. Ombai forms part of Indonesian Archipelagic Sea Lane IIIa; gate is used only for route-transit classification.</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Issue</t>
-  </si>
-  <si>
-    <t>Original Block 2 gate was centered on the PortWatch point (41.3280 N, 140.3533 E) and R045 was sensitive to a -25% shrink.</t>
-  </si>
-  <si>
-    <t>Diagnosis</t>
-  </si>
-  <si>
-    <t>Marine Regions places Tsugaru Strait at 41.499167 N, 140.615833 E (MRGID 33631), materially north-east of the PortWatch point. The pilot SeaRoute segment R045 crosses the strait near this official gazetteer center.</t>
-  </si>
-  <si>
-    <t>Decision</t>
-  </si>
-  <si>
-    <t>Re-center the operational gate on the Marine Regions location while keeping the same 55 km span x 8 km thickness.</t>
-  </si>
-  <si>
-    <t>Geometry status</t>
-  </si>
-  <si>
-    <t>DERIVED (not an official polygon)</t>
-  </si>
-  <si>
-    <t>Base hits</t>
-  </si>
-  <si>
-    <t>R045</t>
-  </si>
-  <si>
-    <t>75% hits</t>
-  </si>
-  <si>
-    <t>125% hits</t>
-  </si>
-  <si>
-    <t>Robustness</t>
-  </si>
-  <si>
-    <t>Stable</t>
-  </si>
-  <si>
-    <t>Interpretation</t>
-  </si>
-  <si>
-    <t>R045 Sabine Pass -&gt; Incheon is retained as a Tsugaru transit in the SeaRoute baseline and is no longer an artifact of the gate size.</t>
-  </si>
-  <si>
     <t>reference</t>
   </si>
   <si>
@@ -1114,6 +869,27 @@
   </si>
   <si>
     <t>NOAA/NCEI geographic reference</t>
+  </si>
+  <si>
+    <t>Yes - detailed Marine Regions geometry</t>
+  </si>
+  <si>
+    <t>FINAL - detailed Marine Regions IHO geometry loaded</t>
+  </si>
+  <si>
+    <t>FINAL - detailed Marine Regions SeaVoX geometry loaded</t>
+  </si>
+  <si>
+    <t>Marine Regions - IHO Sea Areas v3</t>
+  </si>
+  <si>
+    <t>Marine Regions - SeaVoX v19</t>
+  </si>
+  <si>
+    <t>Marine Regions - Detailed geometries received</t>
+  </si>
+  <si>
+    <t>BLOCK 1 v7 - official routeing geometries</t>
   </si>
 </sst>
 </file>
@@ -1135,7 +911,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1149,12 +925,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4B183"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1170,7 +942,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1179,15 +951,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1829,41 +1592,41 @@
         <v>102.6651061</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="J6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="L6">
         <v>4275</v>
       </c>
       <c r="M6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="X6" s="2"/>
       <c r="Y6" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z6" s="2" t="s">
         <v>36</v>
@@ -1871,13 +1634,13 @@
     </row>
     <row r="7" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="D7" s="2">
         <v>26.29685349</v>
@@ -1889,38 +1652,38 @@
         <v>29</v>
       </c>
       <c r="G7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="L7">
         <v>24076</v>
       </c>
       <c r="M7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="N7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="X7" s="2"/>
       <c r="Y7" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="Z7" s="2" t="s">
         <v>36</v>
@@ -1928,13 +1691,13 @@
     </row>
     <row r="8" spans="1:26" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="D8" s="2">
         <v>-34.927285560000001</v>
@@ -1973,13 +1736,13 @@
     </row>
     <row r="9" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="D9" s="2">
         <v>35.942274159999997</v>
@@ -1988,41 +1751,41 @@
         <v>-5.7548957219999997</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="I9" s="2" t="s">
+      <c r="J9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="L9">
         <v>3346</v>
       </c>
       <c r="M9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="X9" s="2"/>
       <c r="Y9" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Z9" s="2" t="s">
         <v>36</v>
@@ -2030,13 +1793,13 @@
     </row>
     <row r="10" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="D10" s="2">
         <v>51.030224140000001</v>
@@ -2045,41 +1808,41 @@
         <v>1.505839717</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="J10" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L10">
         <v>24196</v>
       </c>
       <c r="M10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="N10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O10" t="b">
         <v>1</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="X10" s="2"/>
       <c r="Y10" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="Z10" s="2" t="s">
         <v>36</v>
@@ -2087,13 +1850,13 @@
     </row>
     <row r="11" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D11" s="2">
         <v>55.507840430000002</v>
@@ -2108,25 +1871,25 @@
         <v>30</v>
       </c>
       <c r="H11" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="L11" t="s">
         <v>101</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="M11" t="s">
         <v>102</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="N11" t="s">
         <v>103</v>
-      </c>
-      <c r="L11" t="s">
-        <v>104</v>
-      </c>
-      <c r="M11" t="s">
-        <v>105</v>
-      </c>
-      <c r="N11" t="s">
-        <v>106</v>
       </c>
       <c r="O11" t="b">
         <v>1</v>
@@ -2150,10 +1913,10 @@
         <v>47</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Z11" s="2" t="s">
         <v>49</v>
@@ -2161,13 +1924,13 @@
     </row>
     <row r="12" spans="1:26" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D12" s="2">
         <v>24.723509719999999</v>
@@ -2182,25 +1945,25 @@
         <v>30</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="L12" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="M12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="N12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O12" t="b">
         <v>1</v>
@@ -2224,10 +1987,10 @@
         <v>47</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Z12" s="2" t="s">
         <v>49</v>
@@ -2235,13 +1998,13 @@
     </row>
     <row r="13" spans="1:26" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D13" s="2">
         <v>34.130768109999998</v>
@@ -2256,25 +2019,25 @@
         <v>30</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="M13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="N13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O13" t="b">
         <v>1</v>
@@ -2298,10 +2061,10 @@
         <v>47</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="Z13" s="2" t="s">
         <v>49</v>
@@ -2309,13 +2072,13 @@
     </row>
     <row r="14" spans="1:26" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D14" s="2">
         <v>41.328035989999997</v>
@@ -2330,25 +2093,25 @@
         <v>30</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J14" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="L14" t="s">
+        <v>124</v>
+      </c>
+      <c r="M14" t="s">
+        <v>102</v>
+      </c>
+      <c r="N14" t="s">
         <v>125</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="L14" t="s">
-        <v>127</v>
-      </c>
-      <c r="M14" t="s">
-        <v>105</v>
-      </c>
-      <c r="N14" t="s">
-        <v>128</v>
       </c>
       <c r="O14" t="b">
         <v>1</v>
@@ -2372,10 +2135,10 @@
         <v>47</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="Z14" s="2" t="s">
         <v>49</v>
@@ -2383,13 +2146,13 @@
     </row>
     <row r="15" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D15" s="2">
         <v>20.488890710793999</v>
@@ -2404,25 +2167,25 @@
         <v>30</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L15" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="M15" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="N15" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O15" t="b">
         <v>1</v>
@@ -2446,10 +2209,10 @@
         <v>47</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Z15" s="2" t="s">
         <v>49</v>
@@ -2457,13 +2220,13 @@
     </row>
     <row r="16" spans="1:26" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D16" s="2">
         <v>-8.4191451412925193</v>
@@ -2475,49 +2238,49 @@
         <v>29</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="M16" t="s">
         <v>141</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="N16" t="s">
         <v>142</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="M16" t="s">
-        <v>144</v>
-      </c>
-      <c r="N16" t="s">
-        <v>145</v>
       </c>
       <c r="O16" t="b">
         <v>1</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="X16" s="2"/>
       <c r="Y16" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:26" ht="120" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D17" s="2">
         <v>-8.3985412002436401</v>
@@ -2532,22 +2295,22 @@
         <v>30</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="M17" t="s">
         <v>152</v>
       </c>
-      <c r="J17" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="M17" t="s">
-        <v>155</v>
-      </c>
       <c r="N17" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O17" t="b">
         <v>1</v>
@@ -2571,10 +2334,10 @@
         <v>47</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="Z17" s="2" t="s">
         <v>49</v>
@@ -2582,13 +2345,13 @@
     </row>
     <row r="18" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D18" s="2">
         <v>38.373044249765996</v>
@@ -2603,22 +2366,22 @@
         <v>30</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="M18" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="N18" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O18" t="b">
         <v>1</v>
@@ -2642,10 +2405,10 @@
         <v>47</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="Z18" s="2" t="s">
         <v>49</v>
@@ -2653,13 +2416,13 @@
     </row>
     <row r="19" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D19" s="2">
         <v>-9.8625341319995403</v>
@@ -2674,46 +2437,46 @@
         <v>30</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="M19" t="s">
         <v>167</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="M19" t="s">
-        <v>170</v>
-      </c>
       <c r="N19" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="O19" t="b">
         <v>1</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="X19" s="2"/>
       <c r="Y19" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:26" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D20" s="2">
         <v>-5.9668405704146199</v>
@@ -2725,52 +2488,52 @@
         <v>29</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="L20">
         <v>24127</v>
       </c>
       <c r="M20" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="N20" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="O20" t="b">
         <v>1</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="X20" s="2"/>
       <c r="Y20" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="Z20" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D21" s="2">
         <v>0.352280586988657</v>
@@ -2779,41 +2542,41 @@
         <v>119.257065444388</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="H21" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="I21" s="2" t="s">
+      <c r="J21" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="K21" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="L21">
         <v>4339</v>
       </c>
       <c r="M21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N21" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O21" t="b">
         <v>1</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="X21" s="2"/>
       <c r="Y21" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="Z21" s="2" t="s">
         <v>36</v>
@@ -2821,13 +2584,13 @@
     </row>
     <row r="22" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D22" s="2">
         <v>-52.640339667789199</v>
@@ -2842,25 +2605,25 @@
         <v>30</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="L22">
         <v>9024</v>
       </c>
       <c r="M22" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="N22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O22" t="b">
         <v>1</v>
@@ -2884,10 +2647,10 @@
         <v>47</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="Z22" s="2" t="s">
         <v>49</v>
@@ -2895,13 +2658,13 @@
     </row>
     <row r="23" spans="1:26" ht="75" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D23" s="2">
         <v>21.815254192698799</v>
@@ -2916,22 +2679,22 @@
         <v>30</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="M23" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="N23" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O23" t="b">
         <v>1</v>
@@ -2955,10 +2718,10 @@
         <v>47</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="Z23" s="2" t="s">
         <v>49</v>
@@ -2966,13 +2729,13 @@
     </row>
     <row r="24" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D24" s="2">
         <v>19.986187193207101</v>
@@ -2987,25 +2750,25 @@
         <v>30</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="L24">
         <v>19273</v>
       </c>
       <c r="M24" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="N24" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O24" t="b">
         <v>1</v>
@@ -3029,10 +2792,10 @@
         <v>47</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="Z24" s="2" t="s">
         <v>49</v>
@@ -3040,13 +2803,13 @@
     </row>
     <row r="25" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D25" s="2">
         <v>18.4487355684237</v>
@@ -3061,25 +2824,25 @@
         <v>30</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="L25">
         <v>19526</v>
       </c>
       <c r="M25" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="N25" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O25" t="b">
         <v>1</v>
@@ -3103,10 +2866,10 @@
         <v>47</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="Z25" s="2" t="s">
         <v>49</v>
@@ -3114,13 +2877,13 @@
     </row>
     <row r="26" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D26" s="2">
         <v>7.4136149931776751</v>
@@ -3135,25 +2898,25 @@
         <v>30</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L26">
         <v>21602</v>
       </c>
       <c r="M26" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="N26" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O26" t="b">
         <v>1</v>
@@ -3177,10 +2940,10 @@
         <v>47</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="Z26" s="2" t="s">
         <v>49</v>
@@ -3188,13 +2951,13 @@
     </row>
     <row r="27" spans="1:26" ht="75" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D27" s="2">
         <v>65.96648859155934</v>
@@ -3209,49 +2972,49 @@
         <v>30</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="L27">
         <v>24122</v>
       </c>
       <c r="M27" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N27" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="O27" t="b">
         <v>1</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="X27" s="2"/>
       <c r="Y27" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z27" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D28" s="2">
         <v>12.46831537195925</v>
@@ -3266,25 +3029,25 @@
         <v>30</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="L28">
         <v>14933</v>
       </c>
       <c r="M28" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="N28" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O28" t="b">
         <v>1</v>
@@ -3308,10 +3071,10 @@
         <v>47</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Z28" s="2" t="s">
         <v>49</v>
@@ -3319,13 +3082,13 @@
     </row>
     <row r="29" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D29" s="2">
         <v>45.266763090417008</v>
@@ -3340,25 +3103,25 @@
         <v>30</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="L29">
         <v>3737</v>
       </c>
       <c r="M29" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="N29" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O29" t="b">
         <v>1</v>
@@ -3382,10 +3145,10 @@
         <v>47</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Y29" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Z29" s="2" t="s">
         <v>49</v>
@@ -3407,21 +3170,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>33</v>
@@ -3429,216 +3192,216 @@
     </row>
     <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C8" s="2"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>249</v>
+        <v>284</v>
       </c>
       <c r="B9" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C9" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>252</v>
+        <v>285</v>
       </c>
       <c r="B10" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B11" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C11" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="B12" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C12" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B13" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C13" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B14" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C14" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B15" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C15" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="D18" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="E18" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B19" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C19" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E19" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B20" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="C20" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="D20" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="E20" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>136</v>
+      </c>
+      <c r="B21" t="s">
+        <v>264</v>
+      </c>
+      <c r="C21" t="s">
+        <v>265</v>
+      </c>
+      <c r="D21" t="s">
+        <v>267</v>
+      </c>
+      <c r="E21" t="s">
         <v>139</v>
-      </c>
-      <c r="B21" t="s">
-        <v>271</v>
-      </c>
-      <c r="C21" t="s">
-        <v>272</v>
-      </c>
-      <c r="D21" t="s">
-        <v>274</v>
-      </c>
-      <c r="E21" t="s">
-        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -3647,940 +3410,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>286</v>
-      </c>
-      <c r="B7" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>288</v>
-      </c>
-      <c r="B8" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>290</v>
-      </c>
-      <c r="B9" t="s">
-        <v>291</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="6" width="35" customWidth="1"/>
-    <col min="7" max="7" width="60" customWidth="1"/>
-    <col min="8" max="8" width="65" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="10" width="55" customWidth="1"/>
-    <col min="11" max="11" width="70" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F2" s="2">
-        <v>90</v>
-      </c>
-      <c r="G2" s="2">
-        <v>45</v>
-      </c>
-      <c r="H2" s="2">
-        <v>8</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F3" s="2">
-        <v>135</v>
-      </c>
-      <c r="G3" s="2">
-        <v>220</v>
-      </c>
-      <c r="H3" s="2">
-        <v>12</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F4" s="2">
-        <v>135</v>
-      </c>
-      <c r="G4" s="2">
-        <v>130</v>
-      </c>
-      <c r="H4" s="2">
-        <v>10</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>55</v>
-      </c>
-      <c r="H5" s="2">
-        <v>8</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>220</v>
-      </c>
-      <c r="H6" s="2">
-        <v>12</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="42" customWidth="1"/>
-    <col min="5" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="10" width="55" customWidth="1"/>
-    <col min="11" max="11" width="70" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>115</v>
-      </c>
-      <c r="H2" s="2">
-        <v>12</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>120</v>
-      </c>
-      <c r="H3" s="2">
-        <v>15</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C4" s="2">
-        <v>9024</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>55</v>
-      </c>
-      <c r="H4" s="2">
-        <v>8</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F5" s="2">
-        <v>90</v>
-      </c>
-      <c r="G5" s="2">
-        <v>230</v>
-      </c>
-      <c r="H5" s="2">
-        <v>15</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C6" s="2">
-        <v>19273</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F6" s="2">
-        <v>135</v>
-      </c>
-      <c r="G6" s="2">
-        <v>105</v>
-      </c>
-      <c r="H6" s="2">
-        <v>12</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C7" s="2">
-        <v>19526</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F7" s="2">
-        <v>90</v>
-      </c>
-      <c r="G7" s="2">
-        <v>145</v>
-      </c>
-      <c r="H7" s="2">
-        <v>12</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C8" s="2">
-        <v>21602</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>100</v>
-      </c>
-      <c r="H8" s="2">
-        <v>10</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C9" s="2">
-        <v>14933</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F9" s="2">
-        <v>45</v>
-      </c>
-      <c r="G9" s="2">
-        <v>95</v>
-      </c>
-      <c r="H9" s="2">
-        <v>10</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C10" s="2">
-        <v>3737</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F10" s="2">
-        <v>90</v>
-      </c>
-      <c r="G10" s="2">
-        <v>26</v>
-      </c>
-      <c r="H10" s="2">
-        <v>5</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="110" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4604,31 +3433,31 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>351</v>
+        <v>271</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>352</v>
+        <v>272</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>353</v>
+        <v>273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>354</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>355</v>
+        <v>275</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>322</v>
+        <v>268</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>323</v>
+        <v>269</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>325</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -4639,7 +3468,7 @@
         <v>39</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>357</v>
+        <v>277</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>48</v>
@@ -4664,7 +3493,7 @@
         <v>52</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>357</v>
+        <v>277</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>58</v>
@@ -4683,16 +3512,16 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>357</v>
+        <v>277</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E4" s="2">
         <v>55.507840430000002</v>
@@ -4711,21 +3540,21 @@
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>357</v>
+        <v>277</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E5" s="2">
         <v>24.723509719999999</v>
@@ -4744,21 +3573,21 @@
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>357</v>
+        <v>277</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E6" s="2">
         <v>34.130768109999998</v>
@@ -4777,21 +3606,21 @@
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>357</v>
+        <v>277</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E7" s="2">
         <v>41.499167</v>
@@ -4810,21 +3639,21 @@
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>357</v>
+        <v>277</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E8" s="2">
         <v>20.488890710793999</v>
@@ -4843,21 +3672,21 @@
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>358</v>
+        <v>278</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E9" s="2">
         <v>-8.3985412002436401</v>
@@ -4876,21 +3705,21 @@
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>359</v>
+        <v>279</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E10" s="2">
         <v>38.373044249765996</v>
@@ -4909,21 +3738,21 @@
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>357</v>
+        <v>277</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E11" s="2">
         <v>-52.640339667789199</v>
@@ -4942,21 +3771,21 @@
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>360</v>
+        <v>280</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E12" s="2">
         <v>21.815254192698799</v>
@@ -4975,21 +3804,21 @@
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="E13" s="2">
         <v>19.986187193207101</v>
@@ -5008,21 +3837,21 @@
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="E14" s="2">
         <v>18.4487355684237</v>
@@ -5041,21 +3870,21 @@
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="E15" s="2">
         <v>7.4136149931776751</v>
@@ -5074,21 +3903,21 @@
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>223</v>
       </c>
       <c r="E16" s="2">
         <v>12.46831537195925</v>
@@ -5107,21 +3936,21 @@
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>229</v>
       </c>
       <c r="E17" s="2">
         <v>45.266763090417008</v>
@@ -5140,7 +3969,7 @@
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
